--- a/input_data/Provincia_wage_data_for_private_and_non-private_sector_employment_2018–2020.xlsx
+++ b/input_data/Provincia_wage_data_for_private_and_non-private_sector_employment_2018–2020.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23980"/>
+    <workbookView windowWidth="30240" windowHeight="12920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,85 +27,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>admin</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-更多数据，关注淘宝店【行行文库】
-https://hhwk.taobao.com</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C58" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-更多数据，关注淘宝店【行行文库】
-https://hhwk.taobao.com</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A63" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-更多数据，关注淘宝店【行行文库】
-https://hhwk.taobao.com</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -607,7 +528,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -623,7 +544,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -772,19 +692,8 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="40">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -794,42 +703,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.35"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1167,7 +1040,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1191,16 +1064,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1209,93 +1082,93 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1303,25 +1176,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1868,7 +1726,7 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -1928,7 +1786,7 @@
       <c r="X1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="4" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="4" t="s">
@@ -2021,49 +1879,49 @@
       <c r="BC1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BD1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="7" t="s">
+      <c r="BE1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="8" t="s">
+      <c r="BF1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="8" t="s">
+      <c r="BG1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="8" t="s">
+      <c r="BH1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="8" t="s">
+      <c r="BI1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="BJ1" s="8" t="s">
+      <c r="BJ1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" s="8" t="s">
+      <c r="BK1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="BL1" s="8" t="s">
+      <c r="BL1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="BM1" s="8" t="s">
+      <c r="BM1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="BN1" s="8" t="s">
+      <c r="BN1" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="BO1" s="8" t="s">
+      <c r="BO1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="BP1" s="8" t="s">
+      <c r="BP1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="BQ1" s="8" t="s">
+      <c r="BQ1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="BR1" s="8" t="s">
+      <c r="BR1" s="4" t="s">
         <v>67</v>
       </c>
       <c r="BS1" s="4" t="s">
@@ -2129,121 +1987,121 @@
       <c r="CM1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="CN1" s="9" t="s">
+      <c r="CN1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="CO1" s="9" t="s">
+      <c r="CO1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="CP1" s="9" t="s">
+      <c r="CP1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="CQ1" s="9" t="s">
+      <c r="CQ1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="CR1" s="9" t="s">
+      <c r="CR1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="CS1" s="9" t="s">
+      <c r="CS1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="CT1" s="9" t="s">
+      <c r="CT1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="CU1" s="9" t="s">
+      <c r="CU1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="CV1" s="9" t="s">
+      <c r="CV1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="CW1" s="9" t="s">
+      <c r="CW1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="CX1" s="9" t="s">
+      <c r="CX1" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="CY1" s="9" t="s">
+      <c r="CY1" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="CZ1" s="9" t="s">
+      <c r="CZ1" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="DA1" s="9" t="s">
+      <c r="DA1" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="DB1" s="9" t="s">
+      <c r="DB1" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="DC1" s="9" t="s">
+      <c r="DC1" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="DD1" s="9" t="s">
+      <c r="DD1" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="DE1" s="9" t="s">
+      <c r="DE1" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="DF1" s="9" t="s">
+      <c r="DF1" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="DG1" s="7" t="s">
+      <c r="DG1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="DH1" s="9" t="s">
+      <c r="DH1" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="DI1" s="9" t="s">
+      <c r="DI1" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="DJ1" s="9" t="s">
+      <c r="DJ1" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="DK1" s="9" t="s">
+      <c r="DK1" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="DL1" s="9" t="s">
+      <c r="DL1" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="DM1" s="9" t="s">
+      <c r="DM1" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="DN1" s="9" t="s">
+      <c r="DN1" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="DO1" s="9" t="s">
+      <c r="DO1" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="DP1" s="9" t="s">
+      <c r="DP1" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="DQ1" s="9" t="s">
+      <c r="DQ1" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="DR1" s="9" t="s">
+      <c r="DR1" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="DS1" s="9" t="s">
+      <c r="DS1" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="DT1" s="9" t="s">
+      <c r="DT1" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="DU1" s="9" t="s">
+      <c r="DU1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="DV1" s="9" t="s">
+      <c r="DV1" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="DW1" s="9" t="s">
+      <c r="DW1" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="DX1" s="9" t="s">
+      <c r="DX1" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="DY1" s="9" t="s">
+      <c r="DY1" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="DZ1" s="9" t="s">
+      <c r="DZ1" s="4" t="s">
         <v>125</v>
       </c>
       <c r="EA1" s="4" t="s">
@@ -8440,7 +8298,7 @@
       <c r="DH18" s="3">
         <v>35481</v>
       </c>
-      <c r="DI18" s="10">
+      <c r="DI18" s="5">
         <v>49000</v>
       </c>
       <c r="DJ18" s="3">
@@ -8782,7 +8640,7 @@
       <c r="DH19" s="3">
         <v>63422</v>
       </c>
-      <c r="DI19" s="10">
+      <c r="DI19" s="5">
         <v>57414</v>
       </c>
       <c r="DJ19" s="3">
@@ -20876,25 +20734,25 @@
       <c r="DF52" s="3">
         <v>118812</v>
       </c>
-      <c r="DG52" s="11"/>
-      <c r="DH52" s="11"/>
-      <c r="DI52" s="11"/>
-      <c r="DJ52" s="11"/>
-      <c r="DK52" s="11"/>
-      <c r="DL52" s="11"/>
-      <c r="DM52" s="11"/>
-      <c r="DN52" s="11"/>
-      <c r="DO52" s="11"/>
-      <c r="DP52" s="11"/>
-      <c r="DQ52" s="11"/>
-      <c r="DR52" s="11"/>
-      <c r="DS52" s="11"/>
-      <c r="DT52" s="11"/>
-      <c r="DU52" s="11"/>
-      <c r="DV52" s="11"/>
-      <c r="DW52" s="11"/>
-      <c r="DX52" s="11"/>
-      <c r="DY52" s="11"/>
+      <c r="DG52" s="6"/>
+      <c r="DH52" s="6"/>
+      <c r="DI52" s="6"/>
+      <c r="DJ52" s="6"/>
+      <c r="DK52" s="6"/>
+      <c r="DL52" s="6"/>
+      <c r="DM52" s="6"/>
+      <c r="DN52" s="6"/>
+      <c r="DO52" s="6"/>
+      <c r="DP52" s="6"/>
+      <c r="DQ52" s="6"/>
+      <c r="DR52" s="6"/>
+      <c r="DS52" s="6"/>
+      <c r="DT52" s="6"/>
+      <c r="DU52" s="6"/>
+      <c r="DV52" s="6"/>
+      <c r="DW52" s="6"/>
+      <c r="DX52" s="6"/>
+      <c r="DY52" s="6"/>
       <c r="DZ52" s="3"/>
       <c r="EA52" s="3">
         <v>2.1</v>
@@ -25341,11 +25199,10 @@
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="A1:E1" r:id="rId3" display="行政区划代码"/>
-    <hyperlink ref="E5:I5" r:id="rId3" display="255.3"/>
+    <hyperlink ref="A1:E1" r:id="rId1" display="行政区划代码"/>
+    <hyperlink ref="E5:I5" r:id="rId1" display="255.3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>